--- a/docs/Fase1/Grupal/PLANILLA DE EVALUACIÓN FASE 1.xlsx
+++ b/docs/Fase1/Grupal/PLANILLA DE EVALUACIÓN FASE 1.xlsx
@@ -1,42 +1,61 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29322"/>
   <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F7E6F7D-CEF5-4C7A-B508-380B49CC1D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="EVALUACION1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="RUBRICA" sheetId="2" r:id="rId5"/>
-    <sheet state="hidden" name="ESCALA_IEP" sheetId="3" r:id="rId6"/>
-    <sheet state="hidden" name="ESCALA_PRESENTACION" sheetId="4" r:id="rId7"/>
-    <sheet state="hidden" name="ESCALA_TRAB_EQUIP" sheetId="5" r:id="rId8"/>
-    <sheet state="hidden" name="RELEVANCIA-PUNTAJE" sheetId="6" r:id="rId9"/>
+    <sheet name="EVALUACION1" sheetId="1" r:id="rId1"/>
+    <sheet name="RUBRICA" sheetId="2" r:id="rId2"/>
+    <sheet name="ESCALA_IEP" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="ESCALA_PRESENTACION" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="ESCALA_TRAB_EQUIP" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="RELEVANCIA-PUNTAJE" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="CL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
+    <definedName name="L">'RELEVANCIA-PUNTAJE'!$C$2</definedName>
+    <definedName name="ML">'RELEVANCIA-PUNTAJE'!$D$2</definedName>
+    <definedName name="MR">'RELEVANCIA-PUNTAJE'!$A$3</definedName>
+    <definedName name="MR_CL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
+    <definedName name="MR_L">'RELEVANCIA-PUNTAJE'!$C$3</definedName>
+    <definedName name="MR_ML">'RELEVANCIA-PUNTAJE'!$D$3</definedName>
+    <definedName name="MR_NL">'RELEVANCIA-PUNTAJE'!$E$3</definedName>
     <definedName name="MR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="MR_TL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
+    <definedName name="NL">'RELEVANCIA-PUNTAJE'!$E$2</definedName>
     <definedName name="PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="PR">'RELEVANCIA-PUNTAJE'!$A$5</definedName>
+    <definedName name="PR_ML">'RELEVANCIA-PUNTAJE'!$D$5</definedName>
+    <definedName name="PR_NL">'RELEVANCIA-PUNTAJE'!$E$5</definedName>
     <definedName name="PR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="PR_TL">'RELEVANCIA-PUNTAJE'!$B$5</definedName>
+    <definedName name="RE">'RELEVANCIA-PUNTAJE'!$A$4</definedName>
+    <definedName name="RE_ML">'RELEVANCIA-PUNTAJE'!$D$4</definedName>
+    <definedName name="RE_NL">'RELEVANCIA-PUNTAJE'!$E$4</definedName>
     <definedName name="RE_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
-    <definedName name="NL">'RELEVANCIA-PUNTAJE'!$E$2</definedName>
-    <definedName name="RE_NL">'RELEVANCIA-PUNTAJE'!$E$4</definedName>
+    <definedName name="RE_TL">'RELEVANCIA-PUNTAJE'!$B$4</definedName>
     <definedName name="TL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
-    <definedName name="MR_TL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
-    <definedName name="MR_ML">'RELEVANCIA-PUNTAJE'!$D$3</definedName>
-    <definedName name="PR_NL">'RELEVANCIA-PUNTAJE'!$E$5</definedName>
-    <definedName name="MR_NL">'RELEVANCIA-PUNTAJE'!$E$3</definedName>
-    <definedName name="RE_ML">'RELEVANCIA-PUNTAJE'!$D$4</definedName>
-    <definedName name="L">'RELEVANCIA-PUNTAJE'!$C$2</definedName>
-    <definedName name="PR_ML">'RELEVANCIA-PUNTAJE'!$D$5</definedName>
-    <definedName name="MR_L">'RELEVANCIA-PUNTAJE'!$C$3</definedName>
-    <definedName name="PR_TL">'RELEVANCIA-PUNTAJE'!$B$5</definedName>
-    <definedName name="CL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
-    <definedName name="PR">'RELEVANCIA-PUNTAJE'!$A$5</definedName>
-    <definedName name="RE">'RELEVANCIA-PUNTAJE'!$A$4</definedName>
-    <definedName name="MR_CL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
-    <definedName name="MR">'RELEVANCIA-PUNTAJE'!$A$3</definedName>
-    <definedName name="ML">'RELEVANCIA-PUNTAJE'!$D$2</definedName>
-    <definedName name="RE_TL">'RELEVANCIA-PUNTAJE'!$B$4</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="2NKLeHYUwQruQWB04Lg6btK6x2qtONnFaikiweVXZss="/>
     </ext>
@@ -45,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="99">
   <si>
     <t>INTEGRANTES</t>
   </si>
@@ -60,6 +79,9 @@
   </si>
   <si>
     <t>Lucas Lopez Himsalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jara </t>
   </si>
   <si>
     <t>GRUPAL</t>
@@ -84,6 +106,9 @@
   </si>
   <si>
     <t>No logrado</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
   <si>
     <t>Puntaje</t>
@@ -118,19 +143,19 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Completamente Logrado (</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="10.0"/>
       </rPr>
       <t>100%)</t>
     </r>
@@ -138,19 +163,19 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11.0"/>
       </rPr>
       <t>Logrado</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
-        <b/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">  (60%)</t>
     </r>
@@ -378,88 +403,92 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="15">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font/>
     <font>
-      <sz val="20.0"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF3B3838"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -467,7 +496,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -512,8 +541,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
-    <border/>
+  <borders count="31">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -527,6 +562,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -535,41 +571,38 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color rgb="FF000000"/>
-      </top>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -579,6 +612,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -587,6 +621,9 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -599,48 +636,69 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -652,27 +710,35 @@
       <top style="medium">
         <color rgb="FF7F7F7F"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF7F7F7F"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
@@ -682,6 +748,7 @@
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -690,14 +757,9 @@
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -706,9 +768,11 @@
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -719,27 +783,27 @@
       <bottom style="medium">
         <color rgb="FF7F7F7F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-    </border>
-    <border>
+      <left/>
       <right style="medium">
         <color rgb="FF7F7F7F"/>
       </right>
       <top style="medium">
         <color rgb="FF7F7F7F"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -751,6 +815,8 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -761,6 +827,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -769,6 +836,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -779,6 +847,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -787,9 +856,11 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -800,6 +871,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -808,6 +880,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -818,209 +891,200 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="76">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="2" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="255" vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="15" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="20" fillId="8" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="22" fillId="8" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="13" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="26" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="27" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="28" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="29" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="31" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="33" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1028,38 +1092,46 @@
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1249,1115 +1321,1325 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:K990"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="66.86"/>
-    <col customWidth="1" min="3" max="3" width="22.0"/>
-    <col customWidth="1" min="4" max="4" width="11.29"/>
-    <col customWidth="1" min="5" max="7" width="11.71"/>
-    <col customWidth="1" min="8" max="8" width="7.71"/>
-    <col customWidth="1" min="9" max="9" width="11.71"/>
-    <col customWidth="1" min="10" max="10" width="7.71"/>
-    <col customWidth="1" min="11" max="11" width="11.71"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="66.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="C2" s="1">
         <v>0.75</v>
       </c>
       <c r="D2" s="1">
         <v>0.25</v>
       </c>
-      <c r="E2" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="E3" s="61"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <f>EVALUACION1!$C$23</f>
+        <v>6.6</v>
+      </c>
+      <c r="D4" s="6">
+        <f>$C$34</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="7">
+        <f t="shared" ref="E4:E5" si="0">C4*C$2+D4*D$2</f>
+        <v>6.4499999999999993</v>
+      </c>
+      <c r="G4" s="8"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="4">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6">
+        <f>EVALUACION1!$C$23</f>
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="6">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="0"/>
+        <v>6.4499999999999993</v>
+      </c>
+      <c r="G5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="15" customHeight="1">
+      <c r="B6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="6">
+        <f>EVALUACION1!$C$23</f>
+        <v>6.6</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4.8</v>
+      </c>
+      <c r="E6" s="7">
+        <f t="shared" ref="E6" si="1">C6*C$2+D6*D$2</f>
+        <v>6.1499999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" outlineLevel="1">
+      <c r="A10" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8">
-        <f>$C$34</f>
-        <v>7</v>
-      </c>
-      <c r="E4" s="9">
-        <f t="shared" ref="E4:E5" si="1">C4*C$2+D4*D$2</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="8">
-        <f>EVALUACION1!$C$23</f>
-        <v>7</v>
-      </c>
-      <c r="D5" s="8">
-        <f>C46</f>
-        <v>7</v>
-      </c>
-      <c r="E5" s="9">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="G5" s="10"/>
-    </row>
-    <row r="10" outlineLevel="1">
-      <c r="A10" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
-    </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18" t="s">
+      <c r="D10" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="14" t="s">
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="63"/>
+    </row>
+    <row r="11" spans="1:11" outlineLevel="1">
+      <c r="A11" s="64"/>
+      <c r="B11" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="14" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="14" t="s">
+      <c r="E11" s="63"/>
+      <c r="F11" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="14" t="s">
+      <c r="G11" s="63"/>
+      <c r="H11" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="K11" s="16"/>
-    </row>
-    <row r="12" outlineLevel="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="19" t="str">
+      <c r="I11" s="63"/>
+      <c r="J11" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="63"/>
+    </row>
+    <row r="12" spans="1:11" outlineLevel="1">
+      <c r="A12" s="64"/>
+      <c r="B12" s="11" t="str">
         <f>RUBRICA!A5</f>
         <v>1. Describe brevemente en qué consiste el Proyecto APT, justificando su relevancia para el campo laboral de su carrera.</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="21" t="str">
+      <c r="C12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="13" t="str">
         <f>IF($C12=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="13">
         <f>IF(D12="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F12" s="21" t="str">
+      <c r="F12" s="13" t="str">
         <f>IF($C12=L,"X","")</f>
         <v/>
       </c>
-      <c r="G12" s="21" t="str">
+      <c r="G12" s="13" t="str">
         <f>IF(F12="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H12" s="21" t="str">
+      <c r="H12" s="13" t="str">
         <f>IF($C12=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I12" s="21" t="str">
+      <c r="I12" s="13" t="str">
         <f>IF(H12="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="21" t="str">
+      <c r="J12" s="13" t="str">
         <f>IF($C12=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K12" s="21" t="str">
+      <c r="K12" s="13" t="str">
         <f t="shared" ref="K12:K21" si="2">IF($J12="X",0,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="26.25" customHeight="1" outlineLevel="1">
-      <c r="A13" s="17"/>
-      <c r="B13" s="19" t="str">
+    <row r="13" spans="1:11" ht="26.25" customHeight="1" outlineLevel="1">
+      <c r="A13" s="64"/>
+      <c r="B13" s="11" t="str">
         <f>RUBRICA!A6</f>
         <v>2. Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="21" t="str">
+      <c r="C13" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="13" t="str">
         <f>IF($C13=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="13">
         <f t="shared" ref="E13:E15" si="3">IF(D13="X",100*0.05,"")</f>
         <v>5</v>
       </c>
-      <c r="F13" s="21" t="str">
+      <c r="F13" s="13" t="str">
         <f>IF($C13=L,"X","")</f>
         <v/>
       </c>
-      <c r="G13" s="21" t="str">
+      <c r="G13" s="13" t="str">
         <f t="shared" ref="G13:G15" si="4">IF(F13="X",60*0.05,"")</f>
         <v/>
       </c>
-      <c r="H13" s="21" t="str">
+      <c r="H13" s="13" t="str">
         <f>IF($C13=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I13" s="21" t="str">
+      <c r="I13" s="13" t="str">
         <f t="shared" ref="I13:I15" si="5">IF(H13="X",30*0.05,"")</f>
         <v/>
       </c>
-      <c r="J13" s="21" t="str">
+      <c r="J13" s="13" t="str">
         <f>IF($C13=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K13" s="21" t="str">
+      <c r="K13" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="17"/>
-      <c r="B14" s="19" t="str">
+    <row r="14" spans="1:11" outlineLevel="1">
+      <c r="A14" s="64"/>
+      <c r="B14" s="11" t="str">
         <f>RUBRICA!A8</f>
-        <v>4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="21" t="str">
-        <f>IF($C14=CL,"X","")</f>
+        <v xml:space="preserve">4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="13">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H14" s="13" t="str">
+        <f>IF($C14=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I14" s="13" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J14" s="13" t="str">
+        <f>IF($C14=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K14" s="13" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:11" outlineLevel="1">
+      <c r="A15" s="64"/>
+      <c r="B15" s="11" t="str">
+        <f>RUBRICA!A9</f>
+        <v xml:space="preserve">5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="13" t="str">
+        <f>IF($C15=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E15" s="13">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="F14" s="21" t="str">
-        <f>IF($C14=L,"X","")</f>
+      <c r="F15" s="13" t="str">
+        <f>IF($C15=L,"X","")</f>
         <v/>
       </c>
-      <c r="G14" s="21" t="str">
+      <c r="G15" s="13" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="H14" s="21" t="str">
-        <f>IF($C14=ML,"X","")</f>
+      <c r="H15" s="13" t="str">
+        <f>IF($C15=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I14" s="21" t="str">
+      <c r="I15" s="13" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J14" s="21" t="str">
-        <f>IF($C14=NL,"X","")</f>
+      <c r="J15" s="13" t="str">
+        <f>IF($C15=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K14" s="21" t="str">
+      <c r="K15" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="15" outlineLevel="1">
-      <c r="A15" s="17"/>
-      <c r="B15" s="19" t="str">
-        <f>RUBRICA!A9</f>
-        <v>5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="21" t="str">
-        <f>IF($C15=CL,"X","")</f>
+    <row r="16" spans="1:11" outlineLevel="1">
+      <c r="A16" s="64"/>
+      <c r="B16" s="11" t="str">
+        <f>RUBRICA!A10</f>
+        <v>6. Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="13" t="str">
+        <f>IF($C16=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E15" s="21">
-        <f t="shared" si="3"/>
-        <v>5</v>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f>IF($C15=L,"X","")</f>
+      <c r="E16" s="13">
+        <f t="shared" ref="E16:E17" si="6">IF(D16="X",100*0.1,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F16" s="13" t="str">
+        <f>IF($C16=L,"X","")</f>
         <v/>
       </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
+      <c r="G16" s="13" t="str">
+        <f t="shared" ref="G16:G17" si="7">IF(F16="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H15" s="21" t="str">
-        <f>IF($C15=ML,"X","")</f>
+      <c r="H16" s="13" t="str">
+        <f>IF($C16=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I15" s="21" t="str">
-        <f t="shared" si="5"/>
+      <c r="I16" s="13" t="str">
+        <f t="shared" ref="I16:I17" si="8">IF(H16="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="21" t="str">
-        <f>IF($C15=NL,"X","")</f>
+      <c r="J16" s="13" t="str">
+        <f>IF($C16=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K15" s="21" t="str">
+      <c r="K16" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="17"/>
-      <c r="B16" s="19" t="str">
-        <f>RUBRICA!A10</f>
-        <v>6. Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="21" t="str">
-        <f>IF($C16=CL,"X","")</f>
+    <row r="17" spans="1:11" outlineLevel="1">
+      <c r="A17" s="64"/>
+      <c r="B17" s="11" t="str">
+        <f>RUBRICA!A11</f>
+        <v xml:space="preserve">7. Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades. </v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="13" t="str">
+        <f>IF($C17=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E16" s="21">
-        <f t="shared" ref="E16:E17" si="6">IF(D16="X",100*0.1,"")</f>
+      <c r="E17" s="13">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="F16" s="21" t="str">
-        <f>IF($C16=L,"X","")</f>
+      <c r="F17" s="13" t="str">
+        <f>IF($C17=L,"X","")</f>
         <v/>
       </c>
-      <c r="G16" s="21" t="str">
-        <f t="shared" ref="G16:G17" si="7">IF(F16="X",60*0.1,"")</f>
+      <c r="G17" s="13" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="H16" s="21" t="str">
-        <f>IF($C16=ML,"X","")</f>
+      <c r="H17" s="13" t="str">
+        <f>IF($C17=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I16" s="21" t="str">
-        <f t="shared" ref="I16:I17" si="8">IF(H16="X",30*0.1,"")</f>
+      <c r="I17" s="13" t="str">
+        <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="J16" s="21" t="str">
-        <f>IF($C16=NL,"X","")</f>
+      <c r="J17" s="13" t="str">
+        <f>IF($C17=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K16" s="21" t="str">
+      <c r="K17" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="17" outlineLevel="1">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19" t="str">
-        <f>RUBRICA!A11</f>
-        <v>7. Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades. </v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="21" t="str">
-        <f>IF($C17=CL,"X","")</f>
+    <row r="18" spans="1:11" outlineLevel="1">
+      <c r="A18" s="64"/>
+      <c r="B18" s="11" t="str">
+        <f>RUBRICA!A12</f>
+        <v>8. Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="13" t="str">
+        <f>IF($C18=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E17" s="21">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f>IF($C17=L,"X","")</f>
+      <c r="E18" s="13">
+        <f t="shared" ref="E18:E20" si="9">IF(D18="X",100*0.05,"")</f>
+        <v>5</v>
+      </c>
+      <c r="F18" s="13" t="str">
+        <f>IF($C18=L,"X","")</f>
         <v/>
       </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="7"/>
+      <c r="G18" s="13" t="str">
+        <f t="shared" ref="G18:G20" si="10">IF(F18="X",60*0.05,"")</f>
         <v/>
       </c>
-      <c r="H17" s="21" t="str">
-        <f>IF($C17=ML,"X","")</f>
+      <c r="H18" s="13" t="str">
+        <f>IF($C18=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I17" s="21" t="str">
-        <f t="shared" si="8"/>
+      <c r="I18" s="13" t="str">
+        <f t="shared" ref="I18:I20" si="11">IF(H18="X",30*0.05,"")</f>
         <v/>
       </c>
-      <c r="J17" s="21" t="str">
-        <f>IF($C17=NL,"X","")</f>
+      <c r="J18" s="13" t="str">
+        <f>IF($C18=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K17" s="21" t="str">
+      <c r="K18" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="18" outlineLevel="1">
-      <c r="A18" s="17"/>
-      <c r="B18" s="19" t="str">
-        <f>RUBRICA!A12</f>
-        <v>8. Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="21" t="str">
-        <f>IF($C18=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E18" s="21">
-        <f t="shared" ref="E18:E20" si="9">IF(D18="X",100*0.05,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="21" t="str">
-        <f>IF($C18=L,"X","")</f>
+    <row r="19" spans="1:11" outlineLevel="1">
+      <c r="A19" s="64"/>
+      <c r="B19" s="11" t="str">
+        <f>RUBRICA!A13</f>
+        <v xml:space="preserve">9. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="G18" s="21" t="str">
-        <f t="shared" ref="G18:G20" si="10">IF(F18="X",60*0.05,"")</f>
+      <c r="F19" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="13">
+        <f t="shared" si="10"/>
+        <v>3</v>
+      </c>
+      <c r="H19" s="13" t="str">
+        <f>IF($C19=ML,"X","")</f>
         <v/>
       </c>
-      <c r="H18" s="21" t="str">
-        <f>IF($C18=ML,"X","")</f>
+      <c r="I19" s="13" t="str">
+        <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="I18" s="21" t="str">
-        <f t="shared" ref="I18:I20" si="11">IF(H18="X",30*0.05,"")</f>
+      <c r="J19" s="13" t="str">
+        <f>IF($C19=NL,"X","")</f>
         <v/>
       </c>
-      <c r="J18" s="21" t="str">
-        <f>IF($C18=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K18" s="21" t="str">
+      <c r="K19" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="19" outlineLevel="1">
-      <c r="A19" s="17"/>
-      <c r="B19" s="19" t="str">
-        <f>RUBRICA!A13</f>
-        <v>9. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="21" t="str">
-        <f>IF($C19=CL,"X","")</f>
+    <row r="20" spans="1:11" ht="22.5" customHeight="1" outlineLevel="1">
+      <c r="A20" s="64"/>
+      <c r="B20" s="11" t="str">
+        <f>RUBRICA!A14</f>
+        <v>10. Cumple completando el contenido del informe de presentación del proyecto de acuerdo con la plantilla entregada.</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="13" t="str">
+        <f>IF($C20=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E20" s="13">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="F19" s="21" t="str">
-        <f>IF($C19=L,"X","")</f>
+      <c r="F20" s="13" t="str">
+        <f>IF($C20=L,"X","")</f>
         <v/>
       </c>
-      <c r="G19" s="21" t="str">
+      <c r="G20" s="13" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="H19" s="21" t="str">
-        <f>IF($C19=ML,"X","")</f>
+      <c r="H20" s="13" t="str">
+        <f>IF($C20=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I19" s="21" t="str">
+      <c r="I20" s="13" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J19" s="21" t="str">
-        <f>IF($C19=NL,"X","")</f>
+      <c r="J20" s="13" t="str">
+        <f>IF($C20=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K19" s="21" t="str">
+      <c r="K20" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="20" ht="22.5" customHeight="1" outlineLevel="1">
-      <c r="A20" s="17"/>
-      <c r="B20" s="19" t="str">
-        <f>RUBRICA!A14</f>
-        <v>10. Cumple completando el contenido del informe de presentación del proyecto de acuerdo con la plantilla entregada.</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="21" t="str">
-        <f>IF($C20=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E20" s="21">
-        <f t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="F20" s="21" t="str">
-        <f>IF($C20=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G20" s="21" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="H20" s="21" t="str">
-        <f>IF($C20=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I20" s="21" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="J20" s="21" t="str">
-        <f>IF($C20=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K20" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A21" s="17"/>
-      <c r="B21" s="19" t="str">
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
+      <c r="A21" s="64"/>
+      <c r="B21" s="11" t="str">
         <f>RUBRICA!A16</f>
         <v>12. Desarrolla un plan de trabajo que permita del logro de los objetivos propuestos del proyecto de 
 acuerdo a los tiempos para su desarrollo</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="21" t="str">
+      <c r="C21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="13" t="str">
         <f>IF($C21=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="13">
         <f>IF(D21="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F21" s="21" t="str">
+      <c r="F21" s="13" t="str">
         <f>IF($C21=L,"X","")</f>
         <v/>
       </c>
-      <c r="G21" s="21" t="str">
+      <c r="G21" s="13" t="str">
         <f>IF(F21="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H21" s="21" t="str">
+      <c r="H21" s="13" t="str">
         <f>IF($C21=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I21" s="21" t="str">
+      <c r="I21" s="13" t="str">
         <f>IF(H21="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="21" t="str">
+      <c r="J21" s="13" t="str">
         <f>IF($C21=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K21" s="21" t="str">
+      <c r="K21" s="13" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A22" s="17"/>
-      <c r="B22" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="23">
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
+      <c r="A22" s="64"/>
+      <c r="B22" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="44">
         <f>E22+G22+I22+K22</f>
-        <v>70</v>
-      </c>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24">
+        <v>66</v>
+      </c>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15">
         <f>SUM(E12:E21)</f>
-        <v>70</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24">
+        <v>60</v>
+      </c>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15">
         <f>SUM(G12:G21)</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24">
+        <v>6</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15">
         <f>SUM(I12:I21)</f>
         <v>0</v>
       </c>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24">
+      <c r="J22" s="15"/>
+      <c r="K22" s="15">
         <f>SUM(K12:K21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="26">
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
+      <c r="A23" s="61"/>
+      <c r="B23" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="17">
         <f>VLOOKUP(C22,ESCALA_IEP!A2:B142,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="29" t="str">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A26" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="51" t="str">
         <f>$B$4</f>
         <v>Joaquin Navarro Leyton</v>
       </c>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="31"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="17"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="34"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="17"/>
-      <c r="B28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="14" t="s">
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="66"/>
+    </row>
+    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A27" s="64"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="68"/>
+      <c r="J27" s="68"/>
+      <c r="K27" s="69"/>
+    </row>
+    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A28" s="64"/>
+      <c r="B28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="17"/>
-      <c r="B29" s="35" t="s">
+      <c r="D28" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="14" t="s">
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="63"/>
+    </row>
+    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A29" s="64"/>
+      <c r="B29" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="14" t="s">
+      <c r="C29" s="61"/>
+      <c r="D29" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="G29" s="16"/>
-      <c r="H29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="17"/>
-      <c r="B30" s="19" t="str">
+      <c r="E29" s="63"/>
+      <c r="F29" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="63"/>
+      <c r="J29" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="K29" s="63"/>
+    </row>
+    <row r="30" spans="1:11" ht="24" customHeight="1">
+      <c r="A30" s="64"/>
+      <c r="B30" s="11" t="str">
         <f>RUBRICA!A7</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="21" t="str">
+      <c r="C30" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="13" t="str">
         <f>IF($C30=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="13">
         <f t="shared" ref="E30:E32" si="12">IF(D30="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F30" s="21" t="str">
+      <c r="F30" s="13" t="str">
         <f>IF($C30=L,"X","")</f>
         <v/>
       </c>
-      <c r="G30" s="21" t="str">
+      <c r="G30" s="13" t="str">
         <f t="shared" ref="G30:G32" si="13">IF(F30="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H30" s="21" t="str">
+      <c r="H30" s="13" t="str">
         <f>IF($C30=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I30" s="21" t="str">
+      <c r="I30" s="13" t="str">
         <f t="shared" ref="I30:I32" si="14">IF(H30="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="21" t="str">
+      <c r="J30" s="13" t="str">
         <f>IF($C30=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K30" s="21" t="str">
+      <c r="K30" s="13" t="str">
         <f t="shared" ref="K30:K32" si="15">IF($J30="X",0,"")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="25.5" customHeight="1">
-      <c r="A31" s="17"/>
-      <c r="B31" s="19" t="str">
+    <row r="31" spans="1:11" ht="25.5" customHeight="1">
+      <c r="A31" s="64"/>
+      <c r="B31" s="11" t="str">
         <f>RUBRICA!A15</f>
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="21" t="str">
-        <f>IF($C31=CL,"X","")</f>
+      <c r="C31" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="13">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="H31" s="13" t="str">
+        <f>IF($C31=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I31" s="13" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J31" s="13" t="str">
+        <f>IF($C31=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K31" s="13" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A32" s="64"/>
+      <c r="B32" s="11" t="str">
+        <f>RUBRICA!A17</f>
+        <v>13. Colaboración y trabajo en equipo *</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="13" t="str">
+        <f>IF($C32=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E32" s="13">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="F31" s="21" t="str">
-        <f>IF($C31=L,"X","")</f>
+      <c r="F32" s="13" t="str">
+        <f>IF($C32=L,"X","")</f>
         <v/>
       </c>
-      <c r="G31" s="21" t="str">
+      <c r="G32" s="13" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="H31" s="21" t="str">
-        <f>IF($C31=ML,"X","")</f>
+      <c r="H32" s="13" t="str">
+        <f>IF($C32=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I31" s="21" t="str">
+      <c r="I32" s="13" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="J31" s="21" t="str">
-        <f>IF($C31=NL,"X","")</f>
+      <c r="J32" s="13" t="str">
+        <f>IF($C32=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K31" s="21" t="str">
+      <c r="K32" s="13" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="17"/>
-      <c r="B32" s="19" t="str">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A33" s="64"/>
+      <c r="B33" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="20">
+        <f>E33+G33+I33+K33</f>
+        <v>26</v>
+      </c>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15">
+        <f>SUM(E30:E32)</f>
+        <v>20</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15">
+        <f>SUM(G30:G32)</f>
+        <v>6</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15">
+        <f>SUM(I30:I32)</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15">
+        <f>SUM(K30:K32)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A34" s="61"/>
+      <c r="B34" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="17">
+        <f>VLOOKUP(C33,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1">
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" customHeight="1">
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+    </row>
+    <row r="37" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A38" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="51" t="str">
+        <f>B5</f>
+        <v>Lucas Lopez Himsalam</v>
+      </c>
+      <c r="D38" s="65"/>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
+      <c r="G38" s="65"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="65"/>
+      <c r="J38" s="65"/>
+      <c r="K38" s="66"/>
+    </row>
+    <row r="39" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A39" s="64"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="68"/>
+      <c r="E39" s="68"/>
+      <c r="F39" s="68"/>
+      <c r="G39" s="68"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="68"/>
+      <c r="J39" s="68"/>
+      <c r="K39" s="69"/>
+    </row>
+    <row r="40" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A40" s="64"/>
+      <c r="B40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
+      <c r="J40" s="62"/>
+      <c r="K40" s="63"/>
+    </row>
+    <row r="41" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A41" s="64"/>
+      <c r="B41" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="61"/>
+      <c r="D41" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="63"/>
+      <c r="F41" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="63"/>
+      <c r="H41" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="63"/>
+      <c r="J41" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="63"/>
+    </row>
+    <row r="42" spans="1:11" ht="25.5" customHeight="1">
+      <c r="A42" s="64"/>
+      <c r="B42" s="11" t="str">
+        <f>RUBRICA!A7</f>
+        <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="13" t="str">
+        <f>IF($C42=CL,"X","")</f>
+        <v>X</v>
+      </c>
+      <c r="E42" s="13">
+        <f t="shared" ref="E42:E44" si="16">IF(D42="X",100*0.1,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F42" s="13" t="str">
+        <f>IF($C42=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="str">
+        <f t="shared" ref="G42:G44" si="17">IF(F42="X",60*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="13" t="str">
+        <f>IF($C42=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I42" s="13" t="str">
+        <f t="shared" ref="I42:I44" si="18">IF(H42="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="13" t="str">
+        <f>IF($C42=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K42" s="13" t="str">
+        <f t="shared" ref="K42:K44" si="19">IF($J42="X",0,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A43" s="64"/>
+      <c r="B43" s="11" t="str">
+        <f>RUBRICA!A15</f>
+        <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="13">
+        <f t="shared" si="17"/>
+        <v>6</v>
+      </c>
+      <c r="H43" s="13" t="str">
+        <f>IF($C43=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I43" s="13" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J43" s="13" t="str">
+        <f>IF($C43=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K43" s="13" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A44" s="64"/>
+      <c r="B44" s="11" t="str">
         <f>RUBRICA!A17</f>
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="21" t="str">
-        <f>IF($C32=CL,"X","")</f>
+      <c r="C44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="13" t="str">
+        <f>IF($C44=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E32" s="21">
-        <f t="shared" si="12"/>
-        <v>10</v>
-      </c>
-      <c r="F32" s="21" t="str">
-        <f>IF($C32=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G32" s="21" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="H32" s="21" t="str">
-        <f>IF($C32=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I32" s="21" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J32" s="21" t="str">
-        <f>IF($C32=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K32" s="21" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="17"/>
-      <c r="B33" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="37">
-        <f>E33+G33+I33+K33</f>
-        <v>30</v>
-      </c>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24">
-        <f>SUM(E30:E32)</f>
-        <v>30</v>
-      </c>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24">
-        <f>SUM(G30:G32)</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24">
-        <f>SUM(I30:I32)</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24">
-        <f>SUM(K30:K32)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5"/>
-      <c r="B34" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="26">
-        <f>VLOOKUP(C33,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="B35" s="39"/>
-      <c r="C35" s="40"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="B36" s="39"/>
-      <c r="C36" s="40"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" s="29" t="str">
-        <f>B5</f>
-        <v>Lucas Lopez Himsalam</v>
-      </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
-      <c r="J38" s="30"/>
-      <c r="K38" s="31"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="17"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="33"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="34"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="17"/>
-      <c r="B40" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="16"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="17"/>
-      <c r="B41" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="16"/>
-      <c r="H41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="16"/>
-      <c r="J41" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K41" s="16"/>
-    </row>
-    <row r="42" ht="25.5" customHeight="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="19" t="str">
-        <f>RUBRICA!A7</f>
-        <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="21" t="str">
-        <f>IF($C42=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E42" s="21">
-        <f t="shared" ref="E42:E44" si="16">IF(D42="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F42" s="21" t="str">
-        <f>IF($C42=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G42" s="21" t="str">
-        <f t="shared" ref="G42:G44" si="17">IF(F42="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="21" t="str">
-        <f>IF($C42=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I42" s="21" t="str">
-        <f t="shared" ref="I42:I44" si="18">IF(H42="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="21" t="str">
-        <f>IF($C42=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K42" s="21" t="str">
-        <f t="shared" ref="K42:K44" si="19">IF($J42="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="17"/>
-      <c r="B43" s="19" t="str">
-        <f>RUBRICA!A15</f>
-        <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="21" t="str">
-        <f>IF($C43=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E43" s="21">
+      <c r="E44" s="13">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="F43" s="21" t="str">
-        <f>IF($C43=L,"X","")</f>
+      <c r="F44" s="13" t="str">
+        <f>IF($C44=L,"X","")</f>
         <v/>
       </c>
-      <c r="G43" s="21" t="str">
+      <c r="G44" s="13" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="H43" s="21" t="str">
-        <f>IF($C43=ML,"X","")</f>
+      <c r="H44" s="13" t="str">
+        <f>IF($C44=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I43" s="21" t="str">
+      <c r="I44" s="13" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="J43" s="21" t="str">
-        <f>IF($C43=NL,"X","")</f>
+      <c r="J44" s="13" t="str">
+        <f>IF($C44=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K43" s="21" t="str">
+      <c r="K44" s="13" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="17"/>
-      <c r="B44" s="19" t="str">
+    <row r="45" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A45" s="64"/>
+      <c r="B45" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="20">
+        <f>E45+G45+I45+K45</f>
+        <v>26</v>
+      </c>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15">
+        <f>SUM(E42:E44)</f>
+        <v>20</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15">
+        <f>SUM(G42:G44)</f>
+        <v>6</v>
+      </c>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15">
+        <f>SUM(I42:I44)</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15">
+        <f>SUM(K42:K44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A46" s="61"/>
+      <c r="B46" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="17">
+        <f>VLOOKUP(C45,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15.75" customHeight="1">
+      <c r="B47" s="22"/>
+      <c r="C47" s="23"/>
+    </row>
+    <row r="48" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A48" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="51" t="str">
+        <f>B15</f>
+        <v xml:space="preserve">5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
+      </c>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="66"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A49" s="64"/>
+      <c r="B49" s="61"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="69"/>
+    </row>
+    <row r="50" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A50" s="64"/>
+      <c r="B50" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
+      <c r="J50" s="62"/>
+      <c r="K50" s="63"/>
+    </row>
+    <row r="51" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A51" s="64"/>
+      <c r="B51" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C51" s="61"/>
+      <c r="D51" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="63"/>
+      <c r="F51" s="53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="63"/>
+      <c r="H51" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="63"/>
+      <c r="J51" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" s="63"/>
+    </row>
+    <row r="52" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A52" s="64"/>
+      <c r="B52" s="11" t="str">
         <f>RUBRICA!A17</f>
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
-      <c r="C44" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="21" t="str">
-        <f>IF($C44=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E44" s="21">
-        <f t="shared" si="16"/>
+      <c r="C52" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="21" t="str">
-        <f>IF($C44=L,"X","")</f>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13" t="str">
+        <f t="shared" ref="E52:E54" si="20">IF(D52="X",100*0.1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="21" t="str">
-        <f t="shared" si="17"/>
+      <c r="F52" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="13">
+        <f t="shared" ref="G52:G54" si="21">IF(F52="X",60*0.1,"")</f>
+        <v>6</v>
+      </c>
+      <c r="H52" s="13" t="str">
+        <f>IF($C52=ML,"X","")</f>
         <v/>
       </c>
-      <c r="H44" s="21" t="str">
-        <f>IF($C44=ML,"X","")</f>
+      <c r="I52" s="13" t="str">
+        <f t="shared" ref="I52:I54" si="22">IF(H52="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="I44" s="21" t="str">
-        <f t="shared" si="18"/>
+      <c r="J52" s="13" t="str">
+        <f>IF($C52=NL,"X","")</f>
         <v/>
       </c>
-      <c r="J44" s="21" t="str">
-        <f>IF($C44=NL,"X","")</f>
+      <c r="K52" s="13" t="str">
+        <f t="shared" ref="K52:K54" si="23">IF($J52="X",0,"")</f>
         <v/>
       </c>
-      <c r="K44" s="21" t="str">
-        <f t="shared" si="19"/>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A53" s="64"/>
+      <c r="B53" s="11">
+        <f>RUBRICA!A25</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13" t="str">
+        <f t="shared" si="20"/>
         <v/>
       </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="17"/>
-      <c r="B45" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="C45" s="37">
-        <f>E45+G45+I45+K45</f>
-        <v>30</v>
-      </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24">
-        <f>SUM(E42:E44)</f>
-        <v>30</v>
-      </c>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24">
-        <f>SUM(G42:G44)</f>
+      <c r="F53" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="13">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="H53" s="13" t="str">
+        <f>IF($C53=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I53" s="13" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J53" s="13" t="str">
+        <f>IF($C53=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K53" s="13" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A54" s="64"/>
+      <c r="B54" s="11">
+        <f>RUBRICA!A27</f>
         <v>0</v>
       </c>
-      <c r="H45" s="24"/>
-      <c r="I45" s="24">
-        <f>SUM(I42:I44)</f>
+      <c r="C54" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="13">
+        <f t="shared" si="21"/>
+        <v>6</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J54" s="13" t="str">
+        <f>IF($C54=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K54" s="13" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A55" s="64"/>
+      <c r="B55" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="20">
+        <f>E55+G55+I55+K55</f>
+        <v>18</v>
+      </c>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15">
+        <f>SUM(E52:E54)</f>
         <v>0</v>
       </c>
-      <c r="J45" s="24"/>
-      <c r="K45" s="24">
-        <f>SUM(K42:K44)</f>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15">
+        <f>SUM(G52:G54)</f>
+        <v>18</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15">
+        <f>SUM(I52:I54)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="5"/>
-      <c r="B46" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C46" s="26">
-        <f>VLOOKUP(C45,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" s="39"/>
-      <c r="C47" s="40"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="B48" s="39"/>
-      <c r="C48" s="40"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="39"/>
-      <c r="C49" s="40"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15">
+        <f>SUM(K52:K54)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" customHeight="1">
+      <c r="A56" s="61"/>
+      <c r="B56" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="17">
+        <f>VLOOKUP(C55,ESCALA_TRAB_EQUIP!A12:B72,2,FALSE)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="61" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -3285,7 +3567,7 @@
     <row r="989" ht="15.75" customHeight="1"/>
     <row r="990" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="35">
     <mergeCell ref="A10:A23"/>
     <mergeCell ref="A26:A34"/>
     <mergeCell ref="B26:B27"/>
@@ -3312,377 +3594,401 @@
     <mergeCell ref="F41:G41"/>
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="J41:K41"/>
+    <mergeCell ref="A48:A56"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:K49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:K50"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="J51:K51"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:E5">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4:E5">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:E6">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:E6">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E5">
-      <formula1>1.0</formula1>
-      <formula2>7.0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C12:C21 C30:C32 C42:C44">
-      <formula1>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</formula1>
+  <dataValidations count="1">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E6" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>1</formula1>
+      <formula2>7</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>C12:C21 C30:C32 C42:C44 C52:C54</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="39.43"/>
-    <col customWidth="1" min="2" max="2" width="40.29"/>
-    <col customWidth="1" min="3" max="3" width="31.71"/>
-    <col customWidth="1" min="4" max="4" width="38.71"/>
-    <col customWidth="1" min="5" max="5" width="38.43"/>
-    <col customWidth="1" min="6" max="26" width="11.43"/>
+    <col min="1" max="1" width="39.42578125" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" customWidth="1"/>
+    <col min="5" max="5" width="38.42578125" customWidth="1"/>
+    <col min="6" max="26" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="41" t="s">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A2" s="57" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="46" t="s">
+      <c r="B2" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="47" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A3" s="72"/>
+      <c r="B3" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="45"/>
-    </row>
-    <row r="4" ht="57.0" customHeight="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50">
+      <c r="C3" s="59" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="72"/>
+    </row>
+    <row r="4" spans="1:6" ht="57" customHeight="1">
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="47">
         <v>-0.3</v>
       </c>
-      <c r="E4" s="50">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="49"/>
-    </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="52" t="s">
+      <c r="E4" s="47">
+        <v>0</v>
+      </c>
+      <c r="F4" s="73"/>
+    </row>
+    <row r="5" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A5" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="B5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="C5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="53">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="D5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="E5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="F5" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A6" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="54" t="s">
+      <c r="B6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="C6" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="56">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="7" ht="94.5" customHeight="1">
-      <c r="A7" s="57" t="s">
+      <c r="D6" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="E6" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="F6" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="94.5" customHeight="1">
+      <c r="A7" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="B7" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="57" t="s">
+      <c r="C7" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="58">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="D7" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="E7" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="F7" s="31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A8" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="57" t="s">
+      <c r="B8" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="C8" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="58">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="9" ht="65.25" customHeight="1">
-      <c r="A9" s="51" t="s">
+      <c r="D8" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="E8" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="F8" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="65.25" customHeight="1">
+      <c r="A9" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="B9" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="C9" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="53">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="51" t="s">
+      <c r="D9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="E9" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="52" t="s">
+      <c r="F9" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A10" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="B10" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="C10" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="53">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="54" t="s">
+      <c r="D10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="E10" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="F10" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A11" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="B11" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="54" t="s">
+      <c r="C11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="56">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="59" t="s">
+      <c r="D11" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="55" t="s">
+      <c r="E11" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="F11" s="29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A12" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="B12" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="C12" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="60">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="13" ht="93.75" customHeight="1">
-      <c r="A13" s="57" t="s">
+      <c r="D12" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="E12" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="F12" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="93.75" customHeight="1">
+      <c r="A13" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="B13" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="57" t="s">
+      <c r="C13" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="61">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="57" t="s">
+      <c r="D13" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="E13" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="F13" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A14" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="B14" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="C14" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="61">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="51" t="s">
+      <c r="D14" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="52" t="s">
+      <c r="E14" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="F14" s="34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A15" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="B15" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="52" t="s">
+      <c r="C15" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="53">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="51" t="s">
+      <c r="D15" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="E15" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="F15" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A16" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="52" t="s">
+      <c r="B16" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="52" t="s">
+      <c r="C16" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="53">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="51" t="s">
+      <c r="D16" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="B17" s="52" t="s">
+      <c r="E16" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="52" t="s">
+      <c r="F16" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A17" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="52" t="s">
+      <c r="B17" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="52" t="s">
+      <c r="C17" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="F17" s="53">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="62" t="s">
+      <c r="D17" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="63">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
+      <c r="E17" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A18" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="70"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="20" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="21" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="22" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="23" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="24" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="25" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="26" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:6" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:6" ht="14.25" customHeight="1"/>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
     <row r="35" ht="14.25" customHeight="1"/>
@@ -4653,1168 +4959,1164 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col min="1" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="74">
+        <v>0</v>
+      </c>
+      <c r="B2" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="74">
+        <v>1</v>
+      </c>
+      <c r="B4" s="36">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="74">
+        <v>1.5</v>
+      </c>
+      <c r="B5" s="36">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="74">
+        <v>2</v>
+      </c>
+      <c r="B6" s="36">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="74">
+        <v>2.5</v>
+      </c>
+      <c r="B7" s="36">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="74">
+        <v>3</v>
+      </c>
+      <c r="B8" s="36">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="74">
+        <v>3.5</v>
+      </c>
+      <c r="B9" s="36">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="74">
+        <v>4</v>
+      </c>
+      <c r="B10" s="36">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="74">
+        <v>4.5</v>
+      </c>
+      <c r="B11" s="36">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="74">
+        <v>5</v>
+      </c>
+      <c r="B12" s="36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="74">
+        <v>5.5</v>
+      </c>
+      <c r="B13" s="36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="74">
+        <v>6</v>
+      </c>
+      <c r="B14" s="36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="74">
+        <v>6.5</v>
+      </c>
+      <c r="B15" s="36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="74">
+        <v>7</v>
+      </c>
+      <c r="B16" s="36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="B17" s="36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="74">
+        <v>8</v>
+      </c>
+      <c r="B18" s="36">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="74">
+        <v>8.5</v>
+      </c>
+      <c r="B19" s="36">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="74">
+        <v>9</v>
+      </c>
+      <c r="B20" s="36">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A21" s="74">
+        <v>9.5</v>
+      </c>
+      <c r="B21" s="36">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A22" s="74">
+        <v>10</v>
+      </c>
+      <c r="B22" s="36">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A23" s="74">
+        <v>10.5</v>
+      </c>
+      <c r="B23" s="36">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A24" s="74">
+        <v>11</v>
+      </c>
+      <c r="B24" s="36">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A25" s="74">
+        <v>11.5</v>
+      </c>
+      <c r="B25" s="36">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A26" s="74">
+        <v>12</v>
+      </c>
+      <c r="B26" s="36">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A27" s="74">
+        <v>12.5</v>
+      </c>
+      <c r="B27" s="36">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A28" s="74">
         <v>13</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B28" s="36">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A29" s="74">
+        <v>13.5</v>
+      </c>
+      <c r="B29" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A30" s="74">
         <v>14</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="64">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="65">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="B3" s="65">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="64">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="65">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="64">
-        <v>1.5</v>
-      </c>
-      <c r="B5" s="65">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="64">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="65">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="64">
+      <c r="B30" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A31" s="74">
+        <v>14.5</v>
+      </c>
+      <c r="B31" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A32" s="74">
+        <v>15</v>
+      </c>
+      <c r="B32" s="36">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A33" s="74">
+        <v>15.5</v>
+      </c>
+      <c r="B33" s="36">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A34" s="74">
+        <v>16</v>
+      </c>
+      <c r="B34" s="36">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A35" s="74">
+        <v>16.5</v>
+      </c>
+      <c r="B35" s="36">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A36" s="74">
+        <v>17</v>
+      </c>
+      <c r="B36" s="36">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A37" s="74">
+        <v>17.5</v>
+      </c>
+      <c r="B37" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A38" s="74">
+        <v>18</v>
+      </c>
+      <c r="B38" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A39" s="74">
+        <v>18.5</v>
+      </c>
+      <c r="B39" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A40" s="74">
+        <v>19</v>
+      </c>
+      <c r="B40" s="36">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="74">
+        <v>19.5</v>
+      </c>
+      <c r="B41" s="36">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A42" s="74">
+        <v>20</v>
+      </c>
+      <c r="B42" s="36">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="74">
+        <v>20.5</v>
+      </c>
+      <c r="B43" s="36">
         <v>2.5</v>
       </c>
-      <c r="B7" s="65">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="B8" s="65">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="64">
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="74">
+        <v>21</v>
+      </c>
+      <c r="B44" s="36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="74">
+        <v>21.5</v>
+      </c>
+      <c r="B45" s="36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A46" s="74">
+        <v>22</v>
+      </c>
+      <c r="B46" s="36">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A47" s="74">
+        <v>22.5</v>
+      </c>
+      <c r="B47" s="36">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A48" s="74">
+        <v>23</v>
+      </c>
+      <c r="B48" s="36">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A49" s="74">
+        <v>23.5</v>
+      </c>
+      <c r="B49" s="36">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A50" s="74">
+        <v>24</v>
+      </c>
+      <c r="B50" s="36">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A51" s="74">
+        <v>24.5</v>
+      </c>
+      <c r="B51" s="36">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A52" s="74">
+        <v>25</v>
+      </c>
+      <c r="B52" s="36">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A53" s="74">
+        <v>25.5</v>
+      </c>
+      <c r="B53" s="36">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A54" s="74">
+        <v>26</v>
+      </c>
+      <c r="B54" s="36">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A55" s="74">
+        <v>26.5</v>
+      </c>
+      <c r="B55" s="36">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A56" s="74">
+        <v>27</v>
+      </c>
+      <c r="B56" s="36">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A57" s="74">
+        <v>27.5</v>
+      </c>
+      <c r="B57" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A58" s="74">
+        <v>28</v>
+      </c>
+      <c r="B58" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A59" s="74">
+        <v>28.5</v>
+      </c>
+      <c r="B59" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A60" s="74">
+        <v>29</v>
+      </c>
+      <c r="B60" s="36">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A61" s="74">
+        <v>29.5</v>
+      </c>
+      <c r="B61" s="36">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A62" s="74">
+        <v>30</v>
+      </c>
+      <c r="B62" s="36">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A63" s="74">
+        <v>30.5</v>
+      </c>
+      <c r="B63" s="36">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A64" s="74">
+        <v>31</v>
+      </c>
+      <c r="B64" s="36">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A65" s="74">
+        <v>31.5</v>
+      </c>
+      <c r="B65" s="36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A66" s="74">
+        <v>32</v>
+      </c>
+      <c r="B66" s="36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A67" s="74">
+        <v>32.5</v>
+      </c>
+      <c r="B67" s="36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A68" s="74">
+        <v>33</v>
+      </c>
+      <c r="B68" s="36">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A69" s="74">
+        <v>33.5</v>
+      </c>
+      <c r="B69" s="36">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A70" s="74">
+        <v>34</v>
+      </c>
+      <c r="B70" s="36">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A71" s="74">
+        <v>34.5</v>
+      </c>
+      <c r="B71" s="36">
         <v>3.5</v>
       </c>
-      <c r="B9" s="65">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="64">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="65">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="64">
+    </row>
+    <row r="72" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A72" s="74">
+        <v>35</v>
+      </c>
+      <c r="B72" s="36">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A73" s="74">
+        <v>35.5</v>
+      </c>
+      <c r="B73" s="36">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A74" s="74">
+        <v>36</v>
+      </c>
+      <c r="B74" s="36">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A75" s="74">
+        <v>36.5</v>
+      </c>
+      <c r="B75" s="36">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A76" s="74">
+        <v>37</v>
+      </c>
+      <c r="B76" s="36">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A77" s="74">
+        <v>37.5</v>
+      </c>
+      <c r="B77" s="36">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A78" s="74">
+        <v>38</v>
+      </c>
+      <c r="B78" s="36">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A79" s="74">
+        <v>38.5</v>
+      </c>
+      <c r="B79" s="36">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A80" s="74">
+        <v>39</v>
+      </c>
+      <c r="B80" s="36">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A81" s="74">
+        <v>39.5</v>
+      </c>
+      <c r="B81" s="36">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A82" s="74">
+        <v>40</v>
+      </c>
+      <c r="B82" s="36">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A83" s="74">
+        <v>40.5</v>
+      </c>
+      <c r="B83" s="36">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A84" s="74">
+        <v>41</v>
+      </c>
+      <c r="B84" s="36">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A85" s="74">
+        <v>41.5</v>
+      </c>
+      <c r="B85" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A86" s="74">
+        <v>42</v>
+      </c>
+      <c r="B86" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A87" s="74">
+        <v>42.5</v>
+      </c>
+      <c r="B87" s="36">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A88" s="74">
+        <v>43</v>
+      </c>
+      <c r="B88" s="36">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A89" s="74">
+        <v>43.5</v>
+      </c>
+      <c r="B89" s="36">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A90" s="74">
+        <v>44</v>
+      </c>
+      <c r="B90" s="36">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A91" s="74">
+        <v>44.5</v>
+      </c>
+      <c r="B91" s="36">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A92" s="74">
+        <v>45</v>
+      </c>
+      <c r="B92" s="36">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A93" s="74">
+        <v>45.5</v>
+      </c>
+      <c r="B93" s="36">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A94" s="74">
+        <v>46</v>
+      </c>
+      <c r="B94" s="36">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A95" s="74">
+        <v>46.5</v>
+      </c>
+      <c r="B95" s="36">
         <v>4.5</v>
       </c>
-      <c r="B11" s="65">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="64">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="65">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="64">
+    </row>
+    <row r="96" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A96" s="74">
+        <v>47</v>
+      </c>
+      <c r="B96" s="36">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A97" s="74">
+        <v>47.5</v>
+      </c>
+      <c r="B97" s="36">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A98" s="74">
+        <v>48</v>
+      </c>
+      <c r="B98" s="36">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A99" s="74">
+        <v>48.5</v>
+      </c>
+      <c r="B99" s="36">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A100" s="74">
+        <v>49</v>
+      </c>
+      <c r="B100" s="36">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A101" s="74">
+        <v>49.5</v>
+      </c>
+      <c r="B101" s="36">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A102" s="74">
+        <v>50</v>
+      </c>
+      <c r="B102" s="36">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A103" s="74">
+        <v>50.5</v>
+      </c>
+      <c r="B103" s="36">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A104" s="74">
+        <v>51</v>
+      </c>
+      <c r="B104" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A105" s="74">
+        <v>51.5</v>
+      </c>
+      <c r="B105" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A106" s="74">
+        <v>52</v>
+      </c>
+      <c r="B106" s="36">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A107" s="74">
+        <v>52.5</v>
+      </c>
+      <c r="B107" s="36">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A108" s="74">
+        <v>53</v>
+      </c>
+      <c r="B108" s="36">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A109" s="74">
+        <v>53.5</v>
+      </c>
+      <c r="B109" s="36">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A110" s="74">
+        <v>54</v>
+      </c>
+      <c r="B110" s="36">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A111" s="74">
+        <v>54.5</v>
+      </c>
+      <c r="B111" s="36">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A112" s="74">
+        <v>55</v>
+      </c>
+      <c r="B112" s="36">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A113" s="74">
+        <v>55.5</v>
+      </c>
+      <c r="B113" s="36">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A114" s="74">
+        <v>56</v>
+      </c>
+      <c r="B114" s="36">
         <v>5.5</v>
       </c>
-      <c r="B13" s="65">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="64">
-        <v>6.0</v>
-      </c>
-      <c r="B14" s="65">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="64">
+    </row>
+    <row r="115" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A115" s="74">
+        <v>56.5</v>
+      </c>
+      <c r="B115" s="36">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A116" s="74">
+        <v>57</v>
+      </c>
+      <c r="B116" s="36">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A117" s="74">
+        <v>57.5</v>
+      </c>
+      <c r="B117" s="36">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A118" s="74">
+        <v>58</v>
+      </c>
+      <c r="B118" s="36">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A119" s="74">
+        <v>58.5</v>
+      </c>
+      <c r="B119" s="36">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A120" s="74">
+        <v>59</v>
+      </c>
+      <c r="B120" s="36">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A121" s="74">
+        <v>59.5</v>
+      </c>
+      <c r="B121" s="36">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A122" s="74">
+        <v>60</v>
+      </c>
+      <c r="B122" s="36">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A123" s="74">
+        <v>60.5</v>
+      </c>
+      <c r="B123" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A124" s="74">
+        <v>61</v>
+      </c>
+      <c r="B124" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A125" s="74">
+        <v>61.5</v>
+      </c>
+      <c r="B125" s="36">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A126" s="74">
+        <v>62</v>
+      </c>
+      <c r="B126" s="36">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A127" s="74">
+        <v>62.5</v>
+      </c>
+      <c r="B127" s="36">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A128" s="74">
+        <v>63</v>
+      </c>
+      <c r="B128" s="36">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A129" s="74">
+        <v>63.5</v>
+      </c>
+      <c r="B129" s="36">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A130" s="74">
+        <v>64</v>
+      </c>
+      <c r="B130" s="36">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A131" s="74">
+        <v>64.5</v>
+      </c>
+      <c r="B131" s="36">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A132" s="74">
+        <v>65</v>
+      </c>
+      <c r="B132" s="36">
         <v>6.5</v>
       </c>
-      <c r="B15" s="65">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="64">
-        <v>7.0</v>
-      </c>
-      <c r="B16" s="65">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="64">
-        <v>7.5</v>
-      </c>
-      <c r="B17" s="65">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="64">
-        <v>8.0</v>
-      </c>
-      <c r="B18" s="65">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="64">
-        <v>8.5</v>
-      </c>
-      <c r="B19" s="65">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="64">
-        <v>9.0</v>
-      </c>
-      <c r="B20" s="65">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="64">
-        <v>9.5</v>
-      </c>
-      <c r="B21" s="65">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="64">
-        <v>10.0</v>
-      </c>
-      <c r="B22" s="65">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="64">
-        <v>10.5</v>
-      </c>
-      <c r="B23" s="65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="64">
-        <v>11.0</v>
-      </c>
-      <c r="B24" s="65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="64">
-        <v>11.5</v>
-      </c>
-      <c r="B25" s="65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="64">
-        <v>12.0</v>
-      </c>
-      <c r="B26" s="65">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="64">
-        <v>12.5</v>
-      </c>
-      <c r="B27" s="65">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="64">
-        <v>13.0</v>
-      </c>
-      <c r="B28" s="65">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="64">
-        <v>13.5</v>
-      </c>
-      <c r="B29" s="65">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="64">
-        <v>14.0</v>
-      </c>
-      <c r="B30" s="65">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="64">
-        <v>14.5</v>
-      </c>
-      <c r="B31" s="65">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="64">
-        <v>15.0</v>
-      </c>
-      <c r="B32" s="65">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="64">
-        <v>15.5</v>
-      </c>
-      <c r="B33" s="65">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="64">
-        <v>16.0</v>
-      </c>
-      <c r="B34" s="65">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="64">
-        <v>16.5</v>
-      </c>
-      <c r="B35" s="65">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="64">
-        <v>17.0</v>
-      </c>
-      <c r="B36" s="65">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="64">
-        <v>17.5</v>
-      </c>
-      <c r="B37" s="65">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="64">
-        <v>18.0</v>
-      </c>
-      <c r="B38" s="65">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="64">
-        <v>18.5</v>
-      </c>
-      <c r="B39" s="65">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="64">
-        <v>19.0</v>
-      </c>
-      <c r="B40" s="65">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="64">
-        <v>19.5</v>
-      </c>
-      <c r="B41" s="65">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="64">
-        <v>20.0</v>
-      </c>
-      <c r="B42" s="65">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="64">
-        <v>20.5</v>
-      </c>
-      <c r="B43" s="65">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="64">
-        <v>21.0</v>
-      </c>
-      <c r="B44" s="65">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="64">
-        <v>21.5</v>
-      </c>
-      <c r="B45" s="65">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="64">
-        <v>22.0</v>
-      </c>
-      <c r="B46" s="65">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="64">
-        <v>22.5</v>
-      </c>
-      <c r="B47" s="65">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="64">
-        <v>23.0</v>
-      </c>
-      <c r="B48" s="65">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="64">
-        <v>23.5</v>
-      </c>
-      <c r="B49" s="65">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="64">
-        <v>24.0</v>
-      </c>
-      <c r="B50" s="65">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="64">
-        <v>24.5</v>
-      </c>
-      <c r="B51" s="65">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="64">
-        <v>25.0</v>
-      </c>
-      <c r="B52" s="65">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="64">
-        <v>25.5</v>
-      </c>
-      <c r="B53" s="65">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="64">
-        <v>26.0</v>
-      </c>
-      <c r="B54" s="65">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="64">
-        <v>26.5</v>
-      </c>
-      <c r="B55" s="65">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="64">
-        <v>27.0</v>
-      </c>
-      <c r="B56" s="65">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="64">
-        <v>27.5</v>
-      </c>
-      <c r="B57" s="65">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="64">
-        <v>28.0</v>
-      </c>
-      <c r="B58" s="65">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="64">
-        <v>28.5</v>
-      </c>
-      <c r="B59" s="65">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="64">
-        <v>29.0</v>
-      </c>
-      <c r="B60" s="65">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="64">
-        <v>29.5</v>
-      </c>
-      <c r="B61" s="65">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="64">
-        <v>30.0</v>
-      </c>
-      <c r="B62" s="65">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="64">
-        <v>30.5</v>
-      </c>
-      <c r="B63" s="65">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="64">
-        <v>31.0</v>
-      </c>
-      <c r="B64" s="65">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="64">
-        <v>31.5</v>
-      </c>
-      <c r="B65" s="65">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="64">
-        <v>32.0</v>
-      </c>
-      <c r="B66" s="65">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="64">
-        <v>32.5</v>
-      </c>
-      <c r="B67" s="65">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="64">
-        <v>33.0</v>
-      </c>
-      <c r="B68" s="65">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="64">
-        <v>33.5</v>
-      </c>
-      <c r="B69" s="65">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="64">
-        <v>34.0</v>
-      </c>
-      <c r="B70" s="65">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="64">
-        <v>34.5</v>
-      </c>
-      <c r="B71" s="65">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="64">
-        <v>35.0</v>
-      </c>
-      <c r="B72" s="65">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="64">
-        <v>35.5</v>
-      </c>
-      <c r="B73" s="65">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="64">
-        <v>36.0</v>
-      </c>
-      <c r="B74" s="65">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="64">
-        <v>36.5</v>
-      </c>
-      <c r="B75" s="65">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="64">
-        <v>37.0</v>
-      </c>
-      <c r="B76" s="65">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="64">
-        <v>37.5</v>
-      </c>
-      <c r="B77" s="65">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="64">
-        <v>38.0</v>
-      </c>
-      <c r="B78" s="65">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="64">
-        <v>38.5</v>
-      </c>
-      <c r="B79" s="65">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="64">
-        <v>39.0</v>
-      </c>
-      <c r="B80" s="65">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="64">
-        <v>39.5</v>
-      </c>
-      <c r="B81" s="65">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="64">
-        <v>40.0</v>
-      </c>
-      <c r="B82" s="65">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="64">
-        <v>40.5</v>
-      </c>
-      <c r="B83" s="65">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="64">
-        <v>41.0</v>
-      </c>
-      <c r="B84" s="65">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="64">
-        <v>41.5</v>
-      </c>
-      <c r="B85" s="65">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="64">
-        <v>42.0</v>
-      </c>
-      <c r="B86" s="65">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="64">
-        <v>42.5</v>
-      </c>
-      <c r="B87" s="65">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="64">
-        <v>43.0</v>
-      </c>
-      <c r="B88" s="65">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="64">
-        <v>43.5</v>
-      </c>
-      <c r="B89" s="65">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="64">
-        <v>44.0</v>
-      </c>
-      <c r="B90" s="65">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="64">
-        <v>44.5</v>
-      </c>
-      <c r="B91" s="65">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="64">
-        <v>45.0</v>
-      </c>
-      <c r="B92" s="65">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="64">
-        <v>45.5</v>
-      </c>
-      <c r="B93" s="65">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="64">
-        <v>46.0</v>
-      </c>
-      <c r="B94" s="65">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="64">
-        <v>46.5</v>
-      </c>
-      <c r="B95" s="65">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="64">
-        <v>47.0</v>
-      </c>
-      <c r="B96" s="65">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="64">
-        <v>47.5</v>
-      </c>
-      <c r="B97" s="65">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="64">
-        <v>48.0</v>
-      </c>
-      <c r="B98" s="65">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="64">
-        <v>48.5</v>
-      </c>
-      <c r="B99" s="65">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="64">
-        <v>49.0</v>
-      </c>
-      <c r="B100" s="65">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="64">
-        <v>49.5</v>
-      </c>
-      <c r="B101" s="65">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="64">
-        <v>50.0</v>
-      </c>
-      <c r="B102" s="65">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="64">
-        <v>50.5</v>
-      </c>
-      <c r="B103" s="65">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="64">
-        <v>51.0</v>
-      </c>
-      <c r="B104" s="65">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="64">
-        <v>51.5</v>
-      </c>
-      <c r="B105" s="65">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="64">
-        <v>52.0</v>
-      </c>
-      <c r="B106" s="65">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="64">
-        <v>52.5</v>
-      </c>
-      <c r="B107" s="65">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="64">
-        <v>53.0</v>
-      </c>
-      <c r="B108" s="65">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="64">
-        <v>53.5</v>
-      </c>
-      <c r="B109" s="65">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="64">
-        <v>54.0</v>
-      </c>
-      <c r="B110" s="65">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="64">
-        <v>54.5</v>
-      </c>
-      <c r="B111" s="65">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="64">
-        <v>55.0</v>
-      </c>
-      <c r="B112" s="65">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="64">
-        <v>55.5</v>
-      </c>
-      <c r="B113" s="65">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="64">
-        <v>56.0</v>
-      </c>
-      <c r="B114" s="65">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="64">
-        <v>56.5</v>
-      </c>
-      <c r="B115" s="65">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="64">
-        <v>57.0</v>
-      </c>
-      <c r="B116" s="65">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="64">
-        <v>57.5</v>
-      </c>
-      <c r="B117" s="65">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="64">
-        <v>58.0</v>
-      </c>
-      <c r="B118" s="65">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="64">
-        <v>58.5</v>
-      </c>
-      <c r="B119" s="65">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="64">
-        <v>59.0</v>
-      </c>
-      <c r="B120" s="65">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="64">
-        <v>59.5</v>
-      </c>
-      <c r="B121" s="65">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="64">
-        <v>60.0</v>
-      </c>
-      <c r="B122" s="65">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="64">
-        <v>60.5</v>
-      </c>
-      <c r="B123" s="65">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="64">
-        <v>61.0</v>
-      </c>
-      <c r="B124" s="65">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="64">
-        <v>61.5</v>
-      </c>
-      <c r="B125" s="65">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="64">
-        <v>62.0</v>
-      </c>
-      <c r="B126" s="65">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="64">
-        <v>62.5</v>
-      </c>
-      <c r="B127" s="65">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="64">
-        <v>63.0</v>
-      </c>
-      <c r="B128" s="65">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="64">
-        <v>63.5</v>
-      </c>
-      <c r="B129" s="65">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="64">
-        <v>64.0</v>
-      </c>
-      <c r="B130" s="65">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="64">
-        <v>64.5</v>
-      </c>
-      <c r="B131" s="65">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="64">
-        <v>65.0</v>
-      </c>
-      <c r="B132" s="65">
+    </row>
+    <row r="133" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A133" s="74">
+        <v>65.5</v>
+      </c>
+      <c r="B133" s="36">
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="64">
-        <v>65.5</v>
-      </c>
-      <c r="B133" s="65">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="64">
-        <v>66.0</v>
-      </c>
-      <c r="B134" s="65">
+    <row r="134" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A134" s="74">
+        <v>66</v>
+      </c>
+      <c r="B134" s="36">
         <v>6.6</v>
       </c>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="64">
+    <row r="135" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A135" s="74">
         <v>66.5</v>
       </c>
-      <c r="B135" s="65">
+      <c r="B135" s="36">
         <v>6.6</v>
       </c>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="64">
-        <v>67.0</v>
-      </c>
-      <c r="B136" s="65">
+    <row r="136" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A136" s="74">
+        <v>67</v>
+      </c>
+      <c r="B136" s="36">
         <v>6.7</v>
       </c>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="64">
+    <row r="137" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A137" s="74">
         <v>67.5</v>
       </c>
-      <c r="B137" s="65">
+      <c r="B137" s="36">
         <v>6.7</v>
       </c>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="64">
-        <v>68.0</v>
-      </c>
-      <c r="B138" s="65">
+    <row r="138" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A138" s="74">
+        <v>68</v>
+      </c>
+      <c r="B138" s="36">
         <v>6.8</v>
       </c>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="64">
+    <row r="139" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A139" s="74">
         <v>68.5</v>
       </c>
-      <c r="B139" s="65">
+      <c r="B139" s="36">
         <v>6.8</v>
       </c>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="64">
-        <v>69.0</v>
-      </c>
-      <c r="B140" s="65">
+    <row r="140" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A140" s="74">
+        <v>69</v>
+      </c>
+      <c r="B140" s="36">
         <v>6.9</v>
       </c>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="64">
+    <row r="141" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A141" s="74">
         <v>69.5</v>
       </c>
-      <c r="B141" s="65">
+      <c r="B141" s="36">
         <v>6.9</v>
       </c>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="64">
-        <v>70.0</v>
-      </c>
-      <c r="B142" s="65">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="142" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A142" s="74">
+        <v>70</v>
+      </c>
+      <c r="B142" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="144" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
     <row r="147" ht="15.75" customHeight="1"/>
@@ -6672,465 +6974,461 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col min="1" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="64" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="64" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="64">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="10">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="64">
-        <v>1.0</v>
-      </c>
-      <c r="B3" s="10">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="64">
-        <v>2.0</v>
-      </c>
-      <c r="B4" s="10">
+    <row r="1" spans="1:2">
+      <c r="A1" s="74" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="74">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="74">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="74">
+        <v>2</v>
+      </c>
+      <c r="B4" s="8">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="B5" s="10">
+    <row r="5" spans="1:2">
+      <c r="A5" s="74">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="64">
-        <v>4.0</v>
-      </c>
-      <c r="B6" s="10">
+    <row r="6" spans="1:2">
+      <c r="A6" s="74">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8">
         <v>1.4</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="64">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="10">
+    <row r="7" spans="1:2">
+      <c r="A7" s="74">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8">
         <v>1.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="64">
-        <v>6.0</v>
-      </c>
-      <c r="B8" s="10">
+    <row r="8" spans="1:2">
+      <c r="A8" s="74">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8">
         <v>1.6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="64">
-        <v>7.0</v>
-      </c>
-      <c r="B9" s="10">
+    <row r="9" spans="1:2">
+      <c r="A9" s="74">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8">
         <v>1.7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="64">
-        <v>8.0</v>
-      </c>
-      <c r="B10" s="10">
+    <row r="10" spans="1:2">
+      <c r="A10" s="74">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8">
         <v>1.8</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="64">
-        <v>9.0</v>
-      </c>
-      <c r="B11" s="10">
+    <row r="11" spans="1:2">
+      <c r="A11" s="74">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8">
         <v>1.9</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="64">
-        <v>10.0</v>
-      </c>
-      <c r="B12" s="10">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="64">
-        <v>11.0</v>
-      </c>
-      <c r="B13" s="10">
+    <row r="12" spans="1:2">
+      <c r="A12" s="74">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="74">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8">
         <v>2.1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="64">
-        <v>12.0</v>
-      </c>
-      <c r="B14" s="10">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="64">
-        <v>13.0</v>
-      </c>
-      <c r="B15" s="10">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="64">
-        <v>14.0</v>
-      </c>
-      <c r="B16" s="10">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="64">
-        <v>15.0</v>
-      </c>
-      <c r="B17" s="10">
+    <row r="14" spans="1:2">
+      <c r="A14" s="74">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="74">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="74">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="74">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8">
         <v>2.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="64">
-        <v>16.0</v>
-      </c>
-      <c r="B18" s="10">
+    <row r="18" spans="1:2">
+      <c r="A18" s="74">
+        <v>16</v>
+      </c>
+      <c r="B18" s="8">
         <v>2.5</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="64">
-        <v>17.0</v>
-      </c>
-      <c r="B19" s="10">
+    <row r="19" spans="1:2">
+      <c r="A19" s="74">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8">
         <v>2.6</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="64">
-        <v>18.0</v>
-      </c>
-      <c r="B20" s="10">
+    <row r="20" spans="1:2">
+      <c r="A20" s="74">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8">
         <v>2.7</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="64">
-        <v>19.0</v>
-      </c>
-      <c r="B21" s="10">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A21" s="74">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8">
         <v>2.8</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="64">
-        <v>20.0</v>
-      </c>
-      <c r="B22" s="10">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A22" s="74">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8">
         <v>2.9</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="64">
-        <v>21.0</v>
-      </c>
-      <c r="B23" s="10">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="64">
-        <v>22.0</v>
-      </c>
-      <c r="B24" s="10">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A23" s="74">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A24" s="74">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8">
         <v>3.1</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="64">
-        <v>23.0</v>
-      </c>
-      <c r="B25" s="10">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A25" s="74">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8">
         <v>3.2</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="64">
-        <v>24.0</v>
-      </c>
-      <c r="B26" s="10">
+    <row r="26" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A26" s="74">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8">
         <v>3.3</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="64">
-        <v>25.0</v>
-      </c>
-      <c r="B27" s="10">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A27" s="74">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8">
         <v>3.4</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="64">
-        <v>26.0</v>
-      </c>
-      <c r="B28" s="10">
+    <row r="28" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A28" s="74">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8">
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="64">
-        <v>27.0</v>
-      </c>
-      <c r="B29" s="10">
+    <row r="29" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A29" s="74">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8">
         <v>3.6</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="64">
-        <v>28.0</v>
-      </c>
-      <c r="B30" s="10">
+    <row r="30" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A30" s="74">
+        <v>28</v>
+      </c>
+      <c r="B30" s="8">
         <v>3.7</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="64">
-        <v>29.0</v>
-      </c>
-      <c r="B31" s="10">
+    <row r="31" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A31" s="74">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8">
         <v>3.8</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="64">
-        <v>30.0</v>
-      </c>
-      <c r="B32" s="10">
+    <row r="32" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A32" s="74">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8">
         <v>3.9</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="64">
-        <v>31.0</v>
-      </c>
-      <c r="B33" s="10">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="64">
-        <v>32.0</v>
-      </c>
-      <c r="B34" s="10">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="64">
-        <v>33.0</v>
-      </c>
-      <c r="B35" s="10">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A33" s="74">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A34" s="74">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A35" s="74">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8">
         <v>4.3</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="64">
-        <v>34.0</v>
-      </c>
-      <c r="B36" s="10">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="64">
-        <v>35.0</v>
-      </c>
-      <c r="B37" s="10">
+    <row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A36" s="74">
+        <v>34</v>
+      </c>
+      <c r="B36" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A37" s="74">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8">
         <v>4.5</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="64">
-        <v>36.0</v>
-      </c>
-      <c r="B38" s="10">
+    <row r="38" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A38" s="74">
+        <v>36</v>
+      </c>
+      <c r="B38" s="8">
         <v>4.7</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="64">
-        <v>37.0</v>
-      </c>
-      <c r="B39" s="10">
+    <row r="39" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A39" s="74">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8">
         <v>4.8</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="64">
-        <v>38.0</v>
-      </c>
-      <c r="B40" s="10">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="64">
-        <v>39.0</v>
-      </c>
-      <c r="B41" s="10">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="64">
-        <v>40.0</v>
-      </c>
-      <c r="B42" s="10">
+    <row r="40" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A40" s="74">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="74">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A42" s="74">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8">
         <v>5.3</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="64">
-        <v>41.0</v>
-      </c>
-      <c r="B43" s="10">
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="74">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8">
         <v>5.4</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="64">
-        <v>42.0</v>
-      </c>
-      <c r="B44" s="10">
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="74">
+        <v>42</v>
+      </c>
+      <c r="B44" s="8">
         <v>5.6</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="64">
-        <v>43.0</v>
-      </c>
-      <c r="B45" s="10">
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="74">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8">
         <v>5.7</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="64">
-        <v>44.0</v>
-      </c>
-      <c r="B46" s="10">
+    <row r="46" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A46" s="74">
+        <v>44</v>
+      </c>
+      <c r="B46" s="8">
         <v>5.8</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="64">
-        <v>45.0</v>
-      </c>
-      <c r="B47" s="10">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="64">
-        <v>46.0</v>
-      </c>
-      <c r="B48" s="10">
+    <row r="47" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A47" s="74">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A48" s="74">
+        <v>46</v>
+      </c>
+      <c r="B48" s="8">
         <v>6.1</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="64">
-        <v>47.0</v>
-      </c>
-      <c r="B49" s="10">
+    <row r="49" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A49" s="74">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8">
         <v>6.3</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="64">
-        <v>48.0</v>
-      </c>
-      <c r="B50" s="10">
+    <row r="50" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A50" s="74">
+        <v>48</v>
+      </c>
+      <c r="B50" s="8">
         <v>6.4</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="64">
-        <v>49.0</v>
-      </c>
-      <c r="B51" s="10">
+    <row r="51" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A51" s="74">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8">
         <v>6.6</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="64">
-        <v>50.0</v>
-      </c>
-      <c r="B52" s="10">
+    <row r="52" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A52" s="74">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8">
         <v>6.7</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="64">
-        <v>51.0</v>
-      </c>
-      <c r="B53" s="10">
+    <row r="53" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A53" s="74">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8">
         <v>6.9</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="64">
-        <v>52.0</v>
-      </c>
-      <c r="B54" s="10">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A54" s="74">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="59" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="60" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="61" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -8068,521 +8366,517 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col min="1" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="74" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="74">
+        <v>0</v>
+      </c>
+      <c r="B2" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="36">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="74">
+        <v>1</v>
+      </c>
+      <c r="B4" s="36">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="74">
+        <v>1.5</v>
+      </c>
+      <c r="B5" s="36">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="74">
+        <v>2</v>
+      </c>
+      <c r="B6" s="36">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="74">
+        <v>2.5</v>
+      </c>
+      <c r="B7" s="36">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="74">
+        <v>3</v>
+      </c>
+      <c r="B8" s="36">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="74">
+        <v>3.5</v>
+      </c>
+      <c r="B9" s="36">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="74">
+        <v>4</v>
+      </c>
+      <c r="B10" s="36">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="74">
+        <v>4.5</v>
+      </c>
+      <c r="B11" s="36">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="74">
+        <v>5</v>
+      </c>
+      <c r="B12" s="36">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="74">
+        <v>5.5</v>
+      </c>
+      <c r="B13" s="36">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="74">
+        <v>6</v>
+      </c>
+      <c r="B14" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="74">
+        <v>6.5</v>
+      </c>
+      <c r="B15" s="36">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="74">
+        <v>7</v>
+      </c>
+      <c r="B16" s="36">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="B17" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="74">
+        <v>8</v>
+      </c>
+      <c r="B18" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="74">
+        <v>8.5</v>
+      </c>
+      <c r="B19" s="36">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="74">
+        <v>9</v>
+      </c>
+      <c r="B20" s="36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A21" s="74">
+        <v>9.5</v>
+      </c>
+      <c r="B21" s="36">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A22" s="74">
+        <v>10</v>
+      </c>
+      <c r="B22" s="36">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A23" s="74">
+        <v>10.5</v>
+      </c>
+      <c r="B23" s="36">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A24" s="74">
+        <v>11</v>
+      </c>
+      <c r="B24" s="36">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A25" s="74">
+        <v>11.5</v>
+      </c>
+      <c r="B25" s="36">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A26" s="74">
+        <v>12</v>
+      </c>
+      <c r="B26" s="36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A27" s="74">
+        <v>12.5</v>
+      </c>
+      <c r="B27" s="36">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A28" s="74">
         <v>13</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B28" s="36">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A29" s="74">
+        <v>13.5</v>
+      </c>
+      <c r="B29" s="36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A30" s="74">
         <v>14</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="64">
-        <v>0.0</v>
-      </c>
-      <c r="B2" s="65">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="64">
-        <v>0.5</v>
-      </c>
-      <c r="B3" s="65">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="64">
-        <v>1.0</v>
-      </c>
-      <c r="B4" s="65">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="64">
-        <v>1.5</v>
-      </c>
-      <c r="B5" s="65">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="64">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="65">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="64">
-        <v>2.5</v>
-      </c>
-      <c r="B7" s="65">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="64">
-        <v>3.0</v>
-      </c>
-      <c r="B8" s="65">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="64">
+      <c r="B30" s="36">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A31" s="74">
+        <v>14.5</v>
+      </c>
+      <c r="B31" s="36">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A32" s="74">
+        <v>15</v>
+      </c>
+      <c r="B32" s="36">
         <v>3.5</v>
       </c>
-      <c r="B9" s="65">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="64">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="65">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="64">
+    </row>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A33" s="74">
+        <v>15.5</v>
+      </c>
+      <c r="B33" s="36">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A34" s="74">
+        <v>16</v>
+      </c>
+      <c r="B34" s="36">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A35" s="74">
+        <v>16.5</v>
+      </c>
+      <c r="B35" s="36">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A36" s="74">
+        <v>17</v>
+      </c>
+      <c r="B36" s="36">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A37" s="74">
+        <v>17.5</v>
+      </c>
+      <c r="B37" s="36">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A38" s="74">
+        <v>18</v>
+      </c>
+      <c r="B38" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A39" s="74">
+        <v>18.5</v>
+      </c>
+      <c r="B39" s="36">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A40" s="74">
+        <v>19</v>
+      </c>
+      <c r="B40" s="36">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A41" s="74">
+        <v>19.5</v>
+      </c>
+      <c r="B41" s="36">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A42" s="74">
+        <v>20</v>
+      </c>
+      <c r="B42" s="36">
         <v>4.5</v>
       </c>
-      <c r="B11" s="65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="64">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="65">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="64">
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="74">
+        <v>20.5</v>
+      </c>
+      <c r="B43" s="36">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="74">
+        <v>21</v>
+      </c>
+      <c r="B44" s="36">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="74">
+        <v>21.5</v>
+      </c>
+      <c r="B45" s="36">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A46" s="74">
+        <v>22</v>
+      </c>
+      <c r="B46" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A47" s="74">
+        <v>22.5</v>
+      </c>
+      <c r="B47" s="36">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A48" s="74">
+        <v>23</v>
+      </c>
+      <c r="B48" s="36">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A49" s="74">
+        <v>23.5</v>
+      </c>
+      <c r="B49" s="36">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A50" s="74">
+        <v>24</v>
+      </c>
+      <c r="B50" s="36">
         <v>5.5</v>
       </c>
-      <c r="B13" s="65">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="64">
-        <v>6.0</v>
-      </c>
-      <c r="B14" s="65">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="64">
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A51" s="74">
+        <v>24.5</v>
+      </c>
+      <c r="B51" s="36">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A52" s="74">
+        <v>25</v>
+      </c>
+      <c r="B52" s="36">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A53" s="74">
+        <v>25.5</v>
+      </c>
+      <c r="B53" s="36">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A54" s="74">
+        <v>26</v>
+      </c>
+      <c r="B54" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A55" s="74">
+        <v>26.5</v>
+      </c>
+      <c r="B55" s="36">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A56" s="74">
+        <v>27</v>
+      </c>
+      <c r="B56" s="36">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A57" s="74">
+        <v>27.5</v>
+      </c>
+      <c r="B57" s="36">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A58" s="74">
+        <v>28</v>
+      </c>
+      <c r="B58" s="36">
         <v>6.5</v>
       </c>
-      <c r="B15" s="65">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="64">
-        <v>7.0</v>
-      </c>
-      <c r="B16" s="65">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="64">
-        <v>7.5</v>
-      </c>
-      <c r="B17" s="65">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="64">
-        <v>8.0</v>
-      </c>
-      <c r="B18" s="65">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="64">
-        <v>8.5</v>
-      </c>
-      <c r="B19" s="65">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="64">
-        <v>9.0</v>
-      </c>
-      <c r="B20" s="65">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="64">
-        <v>9.5</v>
-      </c>
-      <c r="B21" s="65">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="64">
-        <v>10.0</v>
-      </c>
-      <c r="B22" s="65">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="64">
-        <v>10.5</v>
-      </c>
-      <c r="B23" s="65">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="64">
-        <v>11.0</v>
-      </c>
-      <c r="B24" s="65">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="64">
-        <v>11.5</v>
-      </c>
-      <c r="B25" s="65">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="64">
-        <v>12.0</v>
-      </c>
-      <c r="B26" s="65">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="64">
-        <v>12.5</v>
-      </c>
-      <c r="B27" s="65">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="64">
-        <v>13.0</v>
-      </c>
-      <c r="B28" s="65">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="64">
-        <v>13.5</v>
-      </c>
-      <c r="B29" s="65">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="64">
-        <v>14.0</v>
-      </c>
-      <c r="B30" s="65">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="64">
-        <v>14.5</v>
-      </c>
-      <c r="B31" s="65">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="64">
-        <v>15.0</v>
-      </c>
-      <c r="B32" s="65">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="64">
-        <v>15.5</v>
-      </c>
-      <c r="B33" s="65">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="64">
-        <v>16.0</v>
-      </c>
-      <c r="B34" s="65">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="64">
-        <v>16.5</v>
-      </c>
-      <c r="B35" s="65">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="64">
-        <v>17.0</v>
-      </c>
-      <c r="B36" s="65">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="64">
-        <v>17.5</v>
-      </c>
-      <c r="B37" s="65">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="64">
-        <v>18.0</v>
-      </c>
-      <c r="B38" s="65">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="64">
-        <v>18.5</v>
-      </c>
-      <c r="B39" s="65">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="64">
-        <v>19.0</v>
-      </c>
-      <c r="B40" s="65">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="64">
-        <v>19.5</v>
-      </c>
-      <c r="B41" s="65">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="64">
-        <v>20.0</v>
-      </c>
-      <c r="B42" s="65">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="64">
-        <v>20.5</v>
-      </c>
-      <c r="B43" s="65">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="64">
-        <v>21.0</v>
-      </c>
-      <c r="B44" s="65">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="64">
-        <v>21.5</v>
-      </c>
-      <c r="B45" s="65">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="64">
-        <v>22.0</v>
-      </c>
-      <c r="B46" s="65">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="64">
-        <v>22.5</v>
-      </c>
-      <c r="B47" s="65">
-        <v>5.1</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="64">
-        <v>23.0</v>
-      </c>
-      <c r="B48" s="65">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="64">
-        <v>23.5</v>
-      </c>
-      <c r="B49" s="65">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="64">
-        <v>24.0</v>
-      </c>
-      <c r="B50" s="65">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="64">
-        <v>24.5</v>
-      </c>
-      <c r="B51" s="65">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="64">
-        <v>25.0</v>
-      </c>
-      <c r="B52" s="65">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="64">
-        <v>25.5</v>
-      </c>
-      <c r="B53" s="65">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="64">
-        <v>26.0</v>
-      </c>
-      <c r="B54" s="65">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="64">
-        <v>26.5</v>
-      </c>
-      <c r="B55" s="65">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="64">
-        <v>27.0</v>
-      </c>
-      <c r="B56" s="65">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="64">
-        <v>27.5</v>
-      </c>
-      <c r="B57" s="65">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="64">
-        <v>28.0</v>
-      </c>
-      <c r="B58" s="65">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="64">
+    </row>
+    <row r="59" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A59" s="74">
         <v>28.5</v>
       </c>
-      <c r="B59" s="65">
+      <c r="B59" s="36">
         <v>6.6</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="64">
-        <v>29.0</v>
-      </c>
-      <c r="B60" s="65">
+    <row r="60" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A60" s="74">
+        <v>29</v>
+      </c>
+      <c r="B60" s="36">
         <v>6.8</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="64">
+    <row r="61" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A61" s="74">
         <v>29.5</v>
       </c>
-      <c r="B61" s="65">
+      <c r="B61" s="36">
         <v>6.9</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="64">
-        <v>30.0</v>
-      </c>
-      <c r="B62" s="65">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="62" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A62" s="74">
+        <v>30</v>
+      </c>
+      <c r="B62" s="36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -9520,79 +9814,75 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="10.71"/>
+    <col min="1" max="6" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="67" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="75"/>
+      <c r="B2" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="69"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="70"/>
-      <c r="B2" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="72" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="72" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="73" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="B3" s="75">
-        <v>4.0</v>
-      </c>
-      <c r="C3" s="75">
-        <v>3.0</v>
-      </c>
-      <c r="D3" s="75">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="75">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="74"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="74"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="75"/>
-      <c r="E5" s="75"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="43">
+        <v>4</v>
+      </c>
+      <c r="C3" s="43">
+        <v>3</v>
+      </c>
+      <c r="D3" s="43">
+        <v>2</v>
+      </c>
+      <c r="E3" s="43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="42"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="42"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -10578,9 +10868,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>